--- a/Entrega_3/Factor R.xlsx
+++ b/Entrega_3/Factor R.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Uandes\11avo_semestre\01-Proyecto_civil\Entrega_3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Uandes\11avo_semestre\Proyecto_civil\Entrega_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4E8C28-620D-40AF-BC72-02225936F29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -660,14 +660,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2137,12 +2137,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="9">
         <v>1</v>
       </c>
@@ -2151,12 +2151,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="9">
         <v>1.2</v>
       </c>
@@ -2288,17 +2288,17 @@
       <c r="D21" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="32"/>
+      <c r="B22" s="31"/>
       <c r="C22">
         <f>C21/D17</f>
         <v>52.171428571428571</v>
@@ -2328,6 +2328,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
@@ -2336,12 +2342,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Entrega_3/Factor R.xlsx
+++ b/Entrega_3/Factor R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Uandes\11avo_semestre\Proyecto_civil\Entrega_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4E8C28-620D-40AF-BC72-02225936F29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE47895-5332-4FA6-9171-AB8E4AD698E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{2653D79F-DE5A-4F93-BBBF-A43AA914CF88}"/>
   </bookViews>
@@ -660,14 +660,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2137,12 +2137,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="9">
         <v>1</v>
       </c>
@@ -2151,12 +2151,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="9">
         <v>1.2</v>
       </c>
@@ -2288,17 +2288,17 @@
       <c r="D21" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="31"/>
+      <c r="B22" s="32"/>
       <c r="C22">
         <f>C21/D17</f>
         <v>52.171428571428571</v>
@@ -2328,12 +2328,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
@@ -2342,6 +2336,12 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3024,8 +3024,8 @@
         <v>90</v>
       </c>
       <c r="K29" s="1">
-        <f>K8*K7*K27/6</f>
-        <v>510.70238046000026</v>
+        <f>K8*K7/6</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>25</v>
